--- a/data/fmsForecastOutput/File1/RPT_RPT9853920998378DH_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT9853920998378DH_fmsForecastOutput.xlsx
@@ -1875,49 +1875,49 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>398.6702681982124</v>
+        <v>398.6702681982122</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>470.0380449862478</v>
+        <v>470.0380449862477</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>516.2316758604552</v>
+        <v>516.2316758604551</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>548.3039295407074</v>
+        <v>548.3039295407073</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>541.4867391151527</v>
+        <v>541.4867391151524</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>398.6702681982124</v>
+        <v>398.6702681982122</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>470.0380449862478</v>
+        <v>470.0380449862477</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>516.2316758604552</v>
+        <v>516.2316758604551</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>548.3039295407074</v>
+        <v>548.3039295407073</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>541.4867391151527</v>
+        <v>541.4867391151524</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>27820.68847244128</v>
+        <v>27820.68847244127</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>26808.57955579338</v>
+        <v>26808.57955579337</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>26688.72125777444</v>
+        <v>26688.72125777443</v>
       </c>
       <c r="P8" s="152" t="n">
         <v>24426.91574912349</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>24358.63224768841</v>
+        <v>24358.6322476884</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,49 +1925,49 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>403.4211358660966</v>
+        <v>403.4211358660964</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>475.6393870695015</v>
+        <v>475.6393870695014</v>
       </c>
       <c r="V8" s="149" t="n">
         <v>522.3834974875542</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>554.8379493029579</v>
+        <v>554.8379493029578</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>547.9395198882881</v>
+        <v>547.939519888288</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>403.4211358660966</v>
+        <v>403.4211358660964</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>475.6393870695015</v>
+        <v>475.6393870695014</v>
       </c>
       <c r="AA8" s="149" t="n">
         <v>522.3834974875542</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>554.8379493029579</v>
+        <v>554.8379493029578</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>547.9395198882881</v>
+        <v>547.939519888288</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>27820.68847244128</v>
+        <v>27820.68847244127</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>26808.57955579338</v>
+        <v>26808.57955579337</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>26688.72125777444</v>
+        <v>26688.72125777443</v>
       </c>
       <c r="AG8" s="152" t="n">
         <v>24426.91574912349</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>24358.63224768841</v>
+        <v>24358.6322476884</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>30831.84816070143</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>33102.1682705018</v>
+        <v>33102.16827050181</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>30831.84816070143</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>33102.1682705018</v>
+        <v>33102.16827050181</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>572.7962582674036</v>
+        <v>572.7962582674035</v>
       </c>
       <c r="D10" s="162" t="n">
         <v>680.5048662816214</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>754.6200758657409</v>
+        <v>754.6200758657407</v>
       </c>
       <c r="F10" s="162" t="n">
         <v>843.7469337014941</v>
@@ -2185,13 +2185,13 @@
         <v>866.8966064284836</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>572.7962582674036</v>
+        <v>572.7962582674035</v>
       </c>
       <c r="I10" s="162" t="n">
         <v>680.5048662816214</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>754.6200758657409</v>
+        <v>754.6200758657407</v>
       </c>
       <c r="K10" s="162" t="n">
         <v>843.7469337014941</v>
@@ -2200,13 +2200,13 @@
         <v>866.8966064284836</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>53828.24471269416</v>
+        <v>53828.24471269414</v>
       </c>
       <c r="N10" s="165" t="n">
         <v>53537.30402299226</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>55426.7699300861</v>
+        <v>55426.76993008608</v>
       </c>
       <c r="P10" s="165" t="n">
         <v>55258.76390982492</v>
@@ -2220,43 +2220,43 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>578.183197173142</v>
+        <v>578.1831971731418</v>
       </c>
       <c r="U10" s="162" t="n">
         <v>686.7880683345556</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>761.4327255641889</v>
+        <v>761.4327255641887</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>851.170271004584</v>
+        <v>851.1702710045839</v>
       </c>
       <c r="X10" s="163" t="n">
         <v>874.510460624344</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>578.183197173142</v>
+        <v>578.1831971731418</v>
       </c>
       <c r="Z10" s="162" t="n">
         <v>686.7880683345556</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>761.4327255641889</v>
+        <v>761.4327255641887</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>851.170271004584</v>
+        <v>851.1702710045839</v>
       </c>
       <c r="AC10" s="163" t="n">
         <v>874.510460624344</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>53828.24471269416</v>
+        <v>53828.24471269414</v>
       </c>
       <c r="AE10" s="165" t="n">
         <v>53537.30402299226</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>55426.7699300861</v>
+        <v>55426.76993008608</v>
       </c>
       <c r="AG10" s="165" t="n">
         <v>55258.76390982492</v>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>925.4686167005007</v>
+        <v>925.4686167005005</v>
       </c>
       <c r="D11" s="156" t="n">
         <v>987.1985745216111</v>
@@ -2327,13 +2327,13 @@
         <v>1056.927784154938</v>
       </c>
       <c r="F11" s="156" t="n">
-        <v>1132.244368632587</v>
+        <v>1132.244368632588</v>
       </c>
       <c r="G11" s="157" t="n">
         <v>1191.55148271664</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>925.4686167005007</v>
+        <v>925.4686167005005</v>
       </c>
       <c r="I11" s="156" t="n">
         <v>987.1985745216111</v>
@@ -2342,13 +2342,13 @@
         <v>1056.927784154938</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>1132.244368632587</v>
+        <v>1132.244368632588</v>
       </c>
       <c r="L11" s="157" t="n">
         <v>1191.55148271664</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>55153.70643224255</v>
+        <v>55153.70643224254</v>
       </c>
       <c r="N11" s="159" t="n">
         <v>65030.68546129684</v>
@@ -2357,7 +2357,7 @@
         <v>76273.81772263565</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>89831.31637886722</v>
+        <v>89831.31637886725</v>
       </c>
       <c r="Q11" s="160" t="n">
         <v>95920.19594081001</v>
@@ -2377,7 +2377,7 @@
         <v>1158.472943390392</v>
       </c>
       <c r="W11" s="156" t="n">
-        <v>1241.025627323945</v>
+        <v>1241.025627323946</v>
       </c>
       <c r="X11" s="157" t="n">
         <v>1306.030718539213</v>
@@ -2392,13 +2392,13 @@
         <v>1158.472943390392</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>1241.025627323945</v>
+        <v>1241.025627323946</v>
       </c>
       <c r="AC11" s="157" t="n">
         <v>1306.030718539213</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>55153.70643224255</v>
+        <v>55153.70643224254</v>
       </c>
       <c r="AE11" s="159" t="n">
         <v>65030.68546129684</v>
@@ -2407,7 +2407,7 @@
         <v>76273.81772263565</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>89831.31637886722</v>
+        <v>89831.31637886725</v>
       </c>
       <c r="AH11" s="160" t="n">
         <v>95920.19594081001</v>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>709.6567859565014</v>
+        <v>709.6567859565013</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>820.2735715841384</v>
+        <v>820.2735715841383</v>
       </c>
       <c r="E12" s="162" t="n">
         <v>904.4407718154124</v>
@@ -2476,10 +2476,10 @@
         <v>1044.946479498633</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>709.6567859565014</v>
+        <v>709.6567859565013</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>820.2735715841384</v>
+        <v>820.2735715841383</v>
       </c>
       <c r="J12" s="162" t="n">
         <v>904.4407718154124</v>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>739.0080736633289</v>
+        <v>739.0080736633287</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>858.8585157415513</v>
+        <v>858.8585157415512</v>
       </c>
       <c r="V12" s="162" t="n">
         <v>949.9965648025516</v>
@@ -2523,13 +2523,13 @@
         <v>1056.694040429</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>1102.268486859472</v>
+        <v>1102.268486859473</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>739.0080736633289</v>
+        <v>739.0080736633287</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>858.8585157415513</v>
+        <v>858.8585157415512</v>
       </c>
       <c r="AA12" s="162" t="n">
         <v>949.9965648025516</v>
@@ -2538,7 +2538,7 @@
         <v>1056.694040429</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>1102.268486859472</v>
+        <v>1102.268486859473</v>
       </c>
       <c r="AD12" s="164" t="n">
         <v>108981.9511449367</v>
@@ -2603,49 +2603,49 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>358.4725784127436</v>
+        <v>358.4725784127435</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>392.3432622461778</v>
+        <v>392.3432622461777</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>433.933742692756</v>
+        <v>433.9337426927559</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>470.3068887369909</v>
+        <v>470.3068887369908</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>512.7856709876891</v>
+        <v>512.7856709876888</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>358.4725784127436</v>
+        <v>358.4725784127435</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>392.3432622461778</v>
+        <v>392.3432622461777</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>433.933742692756</v>
+        <v>433.9337426927559</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>470.3068887369909</v>
+        <v>470.3068887369908</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>512.7856709876891</v>
+        <v>512.7856709876888</v>
       </c>
       <c r="M13" s="158" t="n">
         <v>1551.835907006688</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>1742.588954330176</v>
+        <v>1742.588954330175</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>1985.883866781271</v>
+        <v>1985.88386678127</v>
       </c>
       <c r="P13" s="159" t="n">
         <v>2195.99391004991</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>2442.896018495505</v>
+        <v>2442.896018495504</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>77.44777928670388</v>
+        <v>77.44777928670386</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>84.7655196210878</v>
+        <v>84.76551962108776</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>93.75111724843494</v>
+        <v>93.75111724843492</v>
       </c>
       <c r="W13" s="156" t="n">
         <v>101.6095129987326</v>
@@ -2668,13 +2668,13 @@
         <v>110.7870276825254</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>77.44777928670388</v>
+        <v>77.44777928670386</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>84.7655196210878</v>
+        <v>84.76551962108776</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>93.75111724843494</v>
+        <v>93.75111724843492</v>
       </c>
       <c r="AB13" s="156" t="n">
         <v>101.6095129987326</v>
@@ -2686,16 +2686,16 @@
         <v>1551.835907006688</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>1742.588954330176</v>
+        <v>1742.588954330175</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>1985.883866781271</v>
+        <v>1985.88386678127</v>
       </c>
       <c r="AG13" s="159" t="n">
         <v>2195.99391004991</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>2442.896018495505</v>
+        <v>2442.896018495504</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2755,7 +2755,7 @@
         <v>890.1040500242382</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>985.1875447021812</v>
+        <v>985.1875447021814</v>
       </c>
       <c r="G14" s="169" t="n">
         <v>1028.217747070664</v>
@@ -2770,7 +2770,7 @@
         <v>890.1040500242382</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>985.1875447021812</v>
+        <v>985.1875447021814</v>
       </c>
       <c r="L14" s="169" t="n">
         <v>1028.217747070664</v>
@@ -2785,7 +2785,7 @@
         <v>133686.471519503</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>147286.074198742</v>
+        <v>147286.0741987421</v>
       </c>
       <c r="Q14" s="172" t="n">
         <v>155823.8924774957</v>
@@ -2796,31 +2796,31 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>659.8725840068612</v>
+        <v>659.8725840068611</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>758.5272606822489</v>
+        <v>758.5272606822488</v>
       </c>
       <c r="V14" s="168" t="n">
         <v>836.5065721882397</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>926.8069033239325</v>
+        <v>926.8069033239327</v>
       </c>
       <c r="X14" s="169" t="n">
         <v>966.6453498869624</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>659.8725840068612</v>
+        <v>659.8725840068611</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>758.5272606822489</v>
+        <v>758.5272606822488</v>
       </c>
       <c r="AA14" s="168" t="n">
         <v>836.5065721882397</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>926.8069033239325</v>
+        <v>926.8069033239327</v>
       </c>
       <c r="AC14" s="169" t="n">
         <v>966.6453498869624</v>
@@ -2835,7 +2835,7 @@
         <v>133686.471519503</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>147286.074198742</v>
+        <v>147286.0741987421</v>
       </c>
       <c r="AH14" s="172" t="n">
         <v>155823.8924774957</v>
@@ -4408,49 +4408,49 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>405.8570401836623</v>
+        <v>405.857040183662</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>490.9636863282959</v>
+        <v>490.9636863282958</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>543.4302890512532</v>
+        <v>543.4302890512531</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>584.8282025319799</v>
+        <v>584.8282025319797</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>578.9790234911328</v>
+        <v>578.9790234911326</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>405.8570401836623</v>
+        <v>405.857040183662</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>490.9636863282959</v>
+        <v>490.9636863282958</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>543.4302890512532</v>
+        <v>543.4302890512531</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>584.8282025319799</v>
+        <v>584.8282025319797</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>578.9790234911328</v>
+        <v>578.9790234911326</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>28322.20805009452</v>
+        <v>28322.2080500945</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>28002.07171383925</v>
+        <v>28002.07171383924</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>28094.86551429901</v>
+        <v>28094.865514299</v>
       </c>
       <c r="P35" s="152" t="n">
         <v>26054.0704913905</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>26045.21236363478</v>
+        <v>26045.21236363477</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4458,49 +4458,49 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>410.6935510644614</v>
+        <v>410.6935510644611</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>496.8143947696956</v>
+        <v>496.8143947696955</v>
       </c>
       <c r="V35" s="149" t="n">
         <v>549.9062306901189</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>591.7974741840476</v>
+        <v>591.7974741840475</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>585.8785917371391</v>
+        <v>585.878591737139</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>410.6935510644614</v>
+        <v>410.6935510644611</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>496.8143947696956</v>
+        <v>496.8143947696955</v>
       </c>
       <c r="AA35" s="149" t="n">
         <v>549.9062306901189</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>591.7974741840476</v>
+        <v>591.7974741840475</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>585.8785917371391</v>
+        <v>585.878591737139</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>28322.20805009452</v>
+        <v>28322.2080500945</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>28002.07171383925</v>
+        <v>28002.07171383924</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>28094.86551429901</v>
+        <v>28094.865514299</v>
       </c>
       <c r="AG35" s="152" t="n">
         <v>26054.0704913905</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>26045.21236363478</v>
+        <v>26045.21236363477</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4522,7 +4522,7 @@
         <v>1567.225421588523</v>
       </c>
       <c r="G36" s="157" t="n">
-        <v>1658.548376232081</v>
+        <v>1658.548376232082</v>
       </c>
       <c r="H36" s="155" t="n">
         <v>1088.422091931164</v>
@@ -4537,7 +4537,7 @@
         <v>1567.225421588523</v>
       </c>
       <c r="L36" s="157" t="n">
-        <v>1658.548376232081</v>
+        <v>1658.548376232082</v>
       </c>
       <c r="M36" s="158" t="n">
         <v>26329.80067622504</v>
@@ -4546,13 +4546,13 @@
         <v>27900.96826196151</v>
       </c>
       <c r="O36" s="159" t="n">
-        <v>30211.60156327631</v>
+        <v>30211.6015632763</v>
       </c>
       <c r="P36" s="159" t="n">
         <v>32821.07093582704</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>35324.77891113863</v>
+        <v>35324.77891113864</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>1570.715901369343</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>1662.242247894068</v>
+        <v>1662.242247894069</v>
       </c>
       <c r="Y36" s="155" t="n">
         <v>1090.8461945858</v>
@@ -4587,7 +4587,7 @@
         <v>1570.715901369343</v>
       </c>
       <c r="AC36" s="157" t="n">
-        <v>1662.242247894068</v>
+        <v>1662.242247894069</v>
       </c>
       <c r="AD36" s="158" t="n">
         <v>26329.80067622504</v>
@@ -4596,13 +4596,13 @@
         <v>27900.96826196151</v>
       </c>
       <c r="AF36" s="159" t="n">
-        <v>30211.60156327631</v>
+        <v>30211.6015632763</v>
       </c>
       <c r="AG36" s="159" t="n">
         <v>32821.07093582704</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>35324.77891113863</v>
+        <v>35324.77891113864</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4612,46 +4612,46 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>581.5620827377805</v>
+        <v>581.5620827377803</v>
       </c>
       <c r="D37" s="162" t="n">
         <v>710.5753910792874</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>793.8263525917658</v>
+        <v>793.8263525917656</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>898.965458791675</v>
+        <v>898.9654587916749</v>
       </c>
       <c r="G37" s="163" t="n">
         <v>925.8735815176274</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>581.5620827377805</v>
+        <v>581.5620827377803</v>
       </c>
       <c r="I37" s="162" t="n">
         <v>710.5753910792874</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>793.8263525917658</v>
+        <v>793.8263525917656</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>898.965458791675</v>
+        <v>898.9654587916749</v>
       </c>
       <c r="L37" s="163" t="n">
         <v>925.8735815176274</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>54652.00872631956</v>
+        <v>54652.00872631955</v>
       </c>
       <c r="N37" s="165" t="n">
         <v>55903.03997580076</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>58306.46707757532</v>
+        <v>58306.4670775753</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>58875.14142721755</v>
+        <v>58875.14142721754</v>
       </c>
       <c r="Q37" s="166" t="n">
         <v>61369.99127477341</v>
@@ -4662,46 +4662,46 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>587.0314610103947</v>
+        <v>587.0314610103944</v>
       </c>
       <c r="U37" s="162" t="n">
         <v>717.1362387340436</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>800.9929534211965</v>
+        <v>800.9929534211963</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>906.8746120672453</v>
+        <v>906.8746120672452</v>
       </c>
       <c r="X37" s="163" t="n">
         <v>934.0054237710159</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>587.0314610103947</v>
+        <v>587.0314610103944</v>
       </c>
       <c r="Z37" s="162" t="n">
         <v>717.1362387340436</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>800.9929534211965</v>
+        <v>800.9929534211963</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>906.8746120672453</v>
+        <v>906.8746120672452</v>
       </c>
       <c r="AC37" s="163" t="n">
         <v>934.0054237710159</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>54652.00872631956</v>
+        <v>54652.00872631955</v>
       </c>
       <c r="AE37" s="165" t="n">
         <v>55903.03997580076</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>58306.46707757532</v>
+        <v>58306.4670775753</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>58875.14142721755</v>
+        <v>58875.14142721754</v>
       </c>
       <c r="AH37" s="166" t="n">
         <v>61369.99127477341</v>
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="C38" s="155" t="n">
-        <v>946.2000887448386</v>
+        <v>946.2000887448385</v>
       </c>
       <c r="D38" s="156" t="n">
         <v>1032.705485420063</v>
@@ -4723,13 +4723,13 @@
         <v>1112.37738860219</v>
       </c>
       <c r="F38" s="156" t="n">
-        <v>1205.922877818226</v>
+        <v>1205.922877818227</v>
       </c>
       <c r="G38" s="157" t="n">
         <v>1270.521214318287</v>
       </c>
       <c r="H38" s="155" t="n">
-        <v>946.2000887448386</v>
+        <v>946.2000887448385</v>
       </c>
       <c r="I38" s="156" t="n">
         <v>1032.705485420063</v>
@@ -4738,7 +4738,7 @@
         <v>1112.37738860219</v>
       </c>
       <c r="K38" s="156" t="n">
-        <v>1205.922877818226</v>
+        <v>1205.922877818227</v>
       </c>
       <c r="L38" s="157" t="n">
         <v>1270.521214318287</v>
@@ -4753,7 +4753,7 @@
         <v>80275.37117388066</v>
       </c>
       <c r="P38" s="159" t="n">
-        <v>95676.90735934766</v>
+        <v>95676.90735934769</v>
       </c>
       <c r="Q38" s="160" t="n">
         <v>102277.2793220108</v>
@@ -4803,7 +4803,7 @@
         <v>80275.37117388066</v>
       </c>
       <c r="AG38" s="159" t="n">
-        <v>95676.90735934766</v>
+        <v>95676.90735934769</v>
       </c>
       <c r="AH38" s="160" t="n">
         <v>102277.2793220108</v>
@@ -4816,37 +4816,37 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>723.0660841836251</v>
+        <v>723.0660841836249</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>857.3788794304618</v>
+        <v>857.3788794304617</v>
       </c>
       <c r="E39" s="162" t="n">
         <v>951.6970803368714</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>1067.117987626839</v>
+        <v>1067.11798762684</v>
       </c>
       <c r="G39" s="163" t="n">
         <v>1114.888045047875</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>723.0660841836251</v>
+        <v>723.0660841836249</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>857.3788794304618</v>
+        <v>857.3788794304617</v>
       </c>
       <c r="J39" s="162" t="n">
         <v>951.6970803368714</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>1067.117987626839</v>
+        <v>1067.11798762684</v>
       </c>
       <c r="L39" s="163" t="n">
         <v>1114.888045047875</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>111041.2162899978</v>
+        <v>111041.2162899977</v>
       </c>
       <c r="N39" s="165" t="n">
         <v>123931.4461442882</v>
@@ -4866,10 +4866,10 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>752.9719782551059</v>
+        <v>752.9719782551057</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>897.7092244892217</v>
+        <v>897.7092244892216</v>
       </c>
       <c r="V39" s="162" t="n">
         <v>999.6331271509348</v>
@@ -4881,10 +4881,10 @@
         <v>1176.046795260048</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>752.9719782551059</v>
+        <v>752.9719782551057</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>897.7092244892217</v>
+        <v>897.7092244892216</v>
       </c>
       <c r="AA39" s="162" t="n">
         <v>999.6331271509348</v>
@@ -4896,7 +4896,7 @@
         <v>1176.046795260048</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>111041.2162899978</v>
+        <v>111041.2162899977</v>
       </c>
       <c r="AE39" s="165" t="n">
         <v>123931.4461442882</v>
@@ -4921,37 +4921,37 @@
         <v>320.6687990267246</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>352.2890007084519</v>
+        <v>352.2890007084518</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>387.2241012132338</v>
+        <v>387.2241012132337</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>419.7639390213697</v>
+        <v>419.7639390213696</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>453.9534616845576</v>
+        <v>453.9534616845573</v>
       </c>
       <c r="H40" s="155" t="n">
         <v>320.6687990267246</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>352.2890007084519</v>
+        <v>352.2890007084518</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>387.2241012132338</v>
+        <v>387.2241012132337</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>419.7639390213697</v>
+        <v>419.7639390213696</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>453.9534616845576</v>
+        <v>453.9534616845573</v>
       </c>
       <c r="M40" s="158" t="n">
         <v>1388.182490247327</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>1564.688323821328</v>
+        <v>1564.688323821327</v>
       </c>
       <c r="O40" s="159" t="n">
         <v>1772.11868949475</v>
@@ -4960,7 +4960,7 @@
         <v>1959.99479451594</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>2162.621084936832</v>
+        <v>2162.621084936831</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4968,40 +4968,40 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>69.28029608602077</v>
+        <v>69.28029608602075</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>76.11182114071494</v>
+        <v>76.11182114071489</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>83.65952803989619</v>
+        <v>83.65952803989616</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>90.68973991202434</v>
+        <v>90.68973991202429</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>98.07636517876244</v>
+        <v>98.0763651787624</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>69.28029608602077</v>
+        <v>69.28029608602075</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>76.11182114071494</v>
+        <v>76.11182114071489</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>83.65952803989619</v>
+        <v>83.65952803989616</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>90.68973991202434</v>
+        <v>90.68973991202429</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>98.07636517876244</v>
+        <v>98.0763651787624</v>
       </c>
       <c r="AD40" s="158" t="n">
         <v>1388.182490247327</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>1564.688323821328</v>
+        <v>1564.688323821327</v>
       </c>
       <c r="AF40" s="159" t="n">
         <v>1772.11868949475</v>
@@ -5010,7 +5010,7 @@
         <v>1959.99479451594</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>2162.621084936832</v>
+        <v>2162.621084936831</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5020,10 +5020,10 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>712.0337954935409</v>
+        <v>712.0337954935407</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>842.3216510005188</v>
+        <v>842.3216510005187</v>
       </c>
       <c r="E41" s="180" t="n">
         <v>934.4971416336789</v>
@@ -5035,10 +5035,10 @@
         <v>1094.111246718037</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>712.0337954935409</v>
+        <v>712.0337954935407</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>842.3216510005188</v>
+        <v>842.3216510005187</v>
       </c>
       <c r="J41" s="180" t="n">
         <v>934.4971416336789</v>
@@ -5059,7 +5059,7 @@
         <v>140353.9569409507</v>
       </c>
       <c r="P41" s="183" t="n">
-        <v>156512.0435810811</v>
+        <v>156512.0435810812</v>
       </c>
       <c r="Q41" s="184" t="n">
         <v>165809.8916817211</v>
@@ -5070,31 +5070,31 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>671.1891437917923</v>
+        <v>671.189143791792</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>791.2208580467592</v>
+        <v>791.2208580467591</v>
       </c>
       <c r="V41" s="186" t="n">
         <v>878.2265406459055</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>984.8618970490633</v>
+        <v>984.8618970490635</v>
       </c>
       <c r="X41" s="187" t="n">
         <v>1028.592972560638</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>671.1891437917923</v>
+        <v>671.189143791792</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>791.2208580467592</v>
+        <v>791.2208580467591</v>
       </c>
       <c r="AA41" s="186" t="n">
         <v>878.2265406459055</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>984.8618970490633</v>
+        <v>984.8618970490635</v>
       </c>
       <c r="AC41" s="187" t="n">
         <v>1028.592972560638</v>
@@ -5109,7 +5109,7 @@
         <v>140353.9569409507</v>
       </c>
       <c r="AG41" s="189" t="n">
-        <v>156512.0435810811</v>
+        <v>156512.0435810812</v>
       </c>
       <c r="AH41" s="190" t="n">
         <v>165809.8916817211</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.3021198406140173</v>
+        <v>0.3021198406140171</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.04515711930786145</v>
+        <v>0.04515711930786146</v>
       </c>
       <c r="E57" s="149" t="n">
         <v>0</v>
@@ -6349,10 +6349,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.3021198406140173</v>
+        <v>0.3021198406140171</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.04515711930786145</v>
+        <v>0.04515711930786146</v>
       </c>
       <c r="J57" s="149" t="n">
         <v>0</v>
@@ -6364,10 +6364,10 @@
         <v>0</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>21.08304189588392</v>
+        <v>21.08304189588391</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>2.575532424211909</v>
+        <v>2.57553242421191</v>
       </c>
       <c r="O57" s="152" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.3057201376441581</v>
+        <v>0.305720137644158</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.04569524696675135</v>
+        <v>0.04569524696675136</v>
       </c>
       <c r="V57" s="149" t="n">
         <v>0</v>
@@ -6399,10 +6399,10 @@
         <v>0</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>0.3057201376441581</v>
+        <v>0.305720137644158</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>0.04569524696675135</v>
+        <v>0.04569524696675136</v>
       </c>
       <c r="AA57" s="149" t="n">
         <v>0</v>
@@ -6414,10 +6414,10 @@
         <v>0</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>21.08304189588392</v>
+        <v>21.08304189588391</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>2.575532424211909</v>
+        <v>2.57553242421191</v>
       </c>
       <c r="AF57" s="152" t="n">
         <v>0</v>
@@ -6568,10 +6568,10 @@
         <v>0</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>179.8062269580432</v>
+        <v>179.8062269580431</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>25.44856567806806</v>
+        <v>25.44856567806807</v>
       </c>
       <c r="O59" s="165" t="n">
         <v>0</v>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>1.931345518122091</v>
+        <v>1.93134551812209</v>
       </c>
       <c r="U59" s="162" t="n">
         <v>0.3264596823257928</v>
@@ -6603,7 +6603,7 @@
         <v>0</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>1.931345518122091</v>
+        <v>1.93134551812209</v>
       </c>
       <c r="Z59" s="162" t="n">
         <v>0.3264596823257928</v>
@@ -6618,10 +6618,10 @@
         <v>0</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>179.8062269580432</v>
+        <v>179.8062269580431</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>25.44856567806806</v>
+        <v>25.44856567806807</v>
       </c>
       <c r="AF59" s="165" t="n">
         <v>0</v>
@@ -6772,10 +6772,10 @@
         <v>0</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>179.8062269580432</v>
+        <v>179.8062269580431</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>25.44856567806806</v>
+        <v>25.44856567806807</v>
       </c>
       <c r="O61" s="165" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>1.219268438681356</v>
+        <v>1.219268438681355</v>
       </c>
       <c r="U61" s="162" t="n">
         <v>0.1843391073854133</v>
@@ -6807,7 +6807,7 @@
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>1.219268438681356</v>
+        <v>1.219268438681355</v>
       </c>
       <c r="Z61" s="162" t="n">
         <v>0.1843391073854133</v>
@@ -6822,10 +6822,10 @@
         <v>0</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>179.8062269580432</v>
+        <v>179.8062269580431</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>25.44856567806806</v>
+        <v>25.44856567806807</v>
       </c>
       <c r="AF61" s="165" t="n">
         <v>0</v>
@@ -6976,10 +6976,10 @@
         <v>0</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>179.8062269580432</v>
+        <v>179.8062269580431</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>25.44856567806806</v>
+        <v>25.44856567806807</v>
       </c>
       <c r="O63" s="183" t="n">
         <v>0</v>
@@ -7026,10 +7026,10 @@
         <v>0</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>179.8062269580432</v>
+        <v>179.8062269580431</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>25.44856567806806</v>
+        <v>25.44856567806807</v>
       </c>
       <c r="AF63" s="189" t="n">
         <v>0</v>
@@ -7297,46 +7297,46 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>1.840019621548196</v>
+        <v>1.840019621548195</v>
       </c>
       <c r="D68" s="149" t="n">
         <v>1.239854376999804</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.6309997533837135</v>
+        <v>0.6309997533837133</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.3249907483602633</v>
+        <v>0.3249907483602631</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.3501278464555653</v>
+        <v>0.3501278464555652</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>1.840019621548196</v>
+        <v>1.840019621548195</v>
       </c>
       <c r="I68" s="149" t="n">
         <v>1.239854376999804</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.6309997533837135</v>
+        <v>0.6309997533837133</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.3249907483602633</v>
+        <v>0.3249907483602631</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.3501278464555653</v>
+        <v>0.3501278464555652</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>128.4033868530686</v>
+        <v>128.4033868530685</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>70.71498798436704</v>
+        <v>70.71498798436707</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>32.62212940287412</v>
+        <v>32.62212940287411</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>14.47832342928954</v>
+        <v>14.47832342928953</v>
       </c>
       <c r="Q68" s="153" t="n">
         <v>15.75040501531567</v>
@@ -7347,46 +7347,46 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>1.861946738831845</v>
+        <v>1.861946738831844</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>1.254629454406992</v>
+        <v>1.254629454406993</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.6385192414567573</v>
+        <v>0.638519241456757</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>0.3288635930690607</v>
+        <v>0.3288635930690605</v>
       </c>
       <c r="X68" s="150" t="n">
         <v>0.3543002445450176</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>1.861946738831845</v>
+        <v>1.861946738831844</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>1.254629454406992</v>
+        <v>1.254629454406993</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.6385192414567573</v>
+        <v>0.638519241456757</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.3288635930690607</v>
+        <v>0.3288635930690605</v>
       </c>
       <c r="AC68" s="150" t="n">
         <v>0.3543002445450176</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>128.4033868530686</v>
+        <v>128.4033868530685</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>70.71498798436704</v>
+        <v>70.71498798436707</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>32.62212940287412</v>
+        <v>32.62212940287411</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>14.47832342928954</v>
+        <v>14.47832342928953</v>
       </c>
       <c r="AH68" s="153" t="n">
         <v>15.75040501531567</v>
@@ -7408,10 +7408,10 @@
         <v>3.473079703178348</v>
       </c>
       <c r="F69" s="156" t="n">
-        <v>3.918512959555192</v>
+        <v>3.918512959555193</v>
       </c>
       <c r="G69" s="157" t="n">
-        <v>4.220471598372009</v>
+        <v>4.220471598372007</v>
       </c>
       <c r="H69" s="155" t="n">
         <v>5.14556700413425</v>
@@ -7423,10 +7423,10 @@
         <v>3.473079703178348</v>
       </c>
       <c r="K69" s="156" t="n">
-        <v>3.918512959555192</v>
+        <v>3.918512959555193</v>
       </c>
       <c r="L69" s="157" t="n">
-        <v>4.220471598372009</v>
+        <v>4.220471598372007</v>
       </c>
       <c r="M69" s="158" t="n">
         <v>124.4753800840562</v>
@@ -7438,10 +7438,10 @@
         <v>75.5422104497019</v>
       </c>
       <c r="P69" s="159" t="n">
-        <v>82.06208885902387</v>
+        <v>82.06208885902392</v>
       </c>
       <c r="Q69" s="160" t="n">
-        <v>89.89018846223225</v>
+        <v>89.89018846223222</v>
       </c>
       <c r="S69" s="32" t="inlineStr">
         <is>
@@ -7458,10 +7458,10 @@
         <v>3.480814847283423</v>
       </c>
       <c r="W69" s="156" t="n">
-        <v>3.927240159910548</v>
+        <v>3.92724015991055</v>
       </c>
       <c r="X69" s="157" t="n">
-        <v>4.229871312399563</v>
+        <v>4.229871312399561</v>
       </c>
       <c r="Y69" s="155" t="n">
         <v>5.157027064277088</v>
@@ -7473,10 +7473,10 @@
         <v>3.480814847283423</v>
       </c>
       <c r="AB69" s="156" t="n">
-        <v>3.927240159910548</v>
+        <v>3.92724015991055</v>
       </c>
       <c r="AC69" s="157" t="n">
-        <v>4.229871312399563</v>
+        <v>4.229871312399561</v>
       </c>
       <c r="AD69" s="158" t="n">
         <v>124.4753800840562</v>
@@ -7488,10 +7488,10 @@
         <v>75.5422104497019</v>
       </c>
       <c r="AG69" s="159" t="n">
-        <v>82.06208885902387</v>
+        <v>82.06208885902392</v>
       </c>
       <c r="AH69" s="160" t="n">
-        <v>89.89018846223225</v>
+        <v>89.89018846223222</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" thickTop="1">
@@ -7501,37 +7501,37 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>2.690929497515286</v>
+        <v>2.690929497515285</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>1.749568688366536</v>
+        <v>1.749568688366537</v>
       </c>
       <c r="E70" s="162" t="n">
         <v>1.472627440647828</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>1.474077070914353</v>
+        <v>1.474077070914354</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>1.593772992386109</v>
+        <v>1.593772992386108</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>2.690929497515286</v>
+        <v>2.690929497515285</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>1.749568688366536</v>
+        <v>1.749568688366537</v>
       </c>
       <c r="J70" s="162" t="n">
         <v>1.472627440647828</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>1.474077070914353</v>
+        <v>1.474077070914354</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>1.593772992386109</v>
+        <v>1.593772992386108</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>252.8787669371248</v>
+        <v>252.8787669371247</v>
       </c>
       <c r="N70" s="165" t="n">
         <v>137.6436751878034</v>
@@ -7540,7 +7540,7 @@
         <v>108.164339852576</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>96.54041228831342</v>
+        <v>96.54041228831345</v>
       </c>
       <c r="Q70" s="166" t="n">
         <v>105.6405934775479</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>2.716236703338542</v>
+        <v>2.716236703338541</v>
       </c>
       <c r="U70" s="162" t="n">
         <v>1.765722714765438</v>
@@ -7560,13 +7560,13 @@
         <v>1.485922203416955</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>1.487046091447729</v>
+        <v>1.48704609144773</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>1.607770919123095</v>
+        <v>1.607770919123094</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>2.716236703338542</v>
+        <v>2.716236703338541</v>
       </c>
       <c r="Z70" s="162" t="n">
         <v>1.765722714765438</v>
@@ -7575,13 +7575,13 @@
         <v>1.485922203416955</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>1.487046091447729</v>
+        <v>1.48704609144773</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>1.607770919123095</v>
+        <v>1.607770919123094</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>252.8787669371248</v>
+        <v>252.8787669371247</v>
       </c>
       <c r="AE70" s="165" t="n">
         <v>137.6436751878034</v>
@@ -7590,7 +7590,7 @@
         <v>108.164339852576</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>96.54041228831342</v>
+        <v>96.54041228831345</v>
       </c>
       <c r="AH70" s="166" t="n">
         <v>105.6405934775479</v>
@@ -7609,10 +7609,10 @@
         <v>1.143804330213192</v>
       </c>
       <c r="E71" s="156" t="n">
-        <v>1.527610520250208</v>
+        <v>1.527610520250206</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>2.393468402265412</v>
+        <v>2.393468402265413</v>
       </c>
       <c r="G71" s="157" t="n">
         <v>4.258292614547692</v>
@@ -7624,10 +7624,10 @@
         <v>1.143804330213192</v>
       </c>
       <c r="J71" s="156" t="n">
-        <v>1.527610520250208</v>
+        <v>1.527610520250206</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>2.393468402265412</v>
+        <v>2.393468402265413</v>
       </c>
       <c r="L71" s="157" t="n">
         <v>4.258292614547692</v>
@@ -7636,10 +7636,10 @@
         <v>51.28127016427074</v>
       </c>
       <c r="N71" s="159" t="n">
-        <v>75.3469277074357</v>
+        <v>75.34692770743568</v>
       </c>
       <c r="O71" s="159" t="n">
-        <v>110.2409153392683</v>
+        <v>110.2409153392682</v>
       </c>
       <c r="P71" s="159" t="n">
         <v>189.8957709512762</v>
@@ -7656,13 +7656,13 @@
         <v>0.9431621134010063</v>
       </c>
       <c r="U71" s="156" t="n">
-        <v>1.253696221207965</v>
+        <v>1.253696221207964</v>
       </c>
       <c r="V71" s="156" t="n">
-        <v>1.674376889584125</v>
+        <v>1.674376889584123</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>2.623422741319329</v>
+        <v>2.62342274131933</v>
       </c>
       <c r="X71" s="157" t="n">
         <v>4.667411390776225</v>
@@ -7671,13 +7671,13 @@
         <v>0.9431621134010063</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>1.253696221207965</v>
+        <v>1.253696221207964</v>
       </c>
       <c r="AA71" s="156" t="n">
-        <v>1.674376889584125</v>
+        <v>1.674376889584123</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>2.623422741319329</v>
+        <v>2.62342274131933</v>
       </c>
       <c r="AC71" s="157" t="n">
         <v>4.667411390776225</v>
@@ -7686,10 +7686,10 @@
         <v>51.28127016427074</v>
       </c>
       <c r="AE71" s="159" t="n">
-        <v>75.3469277074357</v>
+        <v>75.34692770743568</v>
       </c>
       <c r="AF71" s="159" t="n">
-        <v>110.2409153392683</v>
+        <v>110.2409153392682</v>
       </c>
       <c r="AG71" s="159" t="n">
         <v>189.8957709512762</v>
@@ -7711,7 +7711,7 @@
         <v>1.473505313792023</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>1.499876508487026</v>
+        <v>1.499876508487025</v>
       </c>
       <c r="F72" s="162" t="n">
         <v>1.977723400252419</v>
@@ -7726,7 +7726,7 @@
         <v>1.473505313792023</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>1.499876508487026</v>
+        <v>1.499876508487025</v>
       </c>
       <c r="K72" s="162" t="n">
         <v>1.977723400252419</v>
@@ -7741,10 +7741,10 @@
         <v>212.9906028952391</v>
       </c>
       <c r="O72" s="165" t="n">
-        <v>218.4052551918443</v>
+        <v>218.4052551918442</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>286.4361832395896</v>
+        <v>286.4361832395897</v>
       </c>
       <c r="Q72" s="166" t="n">
         <v>448.434226724071</v>
@@ -7755,31 +7755,31 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>2.062513294561363</v>
+        <v>2.062513294561362</v>
       </c>
       <c r="U72" s="162" t="n">
         <v>1.542817702021862</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>1.575423814464573</v>
+        <v>1.575423814464572</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>2.086120616862688</v>
+        <v>2.086120616862689</v>
       </c>
       <c r="X72" s="163" t="n">
         <v>3.222660746497809</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>2.062513294561363</v>
+        <v>2.062513294561362</v>
       </c>
       <c r="Z72" s="162" t="n">
         <v>1.542817702021862</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>1.575423814464573</v>
+        <v>1.575423814464572</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>2.086120616862688</v>
+        <v>2.086120616862689</v>
       </c>
       <c r="AC72" s="163" t="n">
         <v>3.222660746497809</v>
@@ -7791,10 +7791,10 @@
         <v>212.9906028952391</v>
       </c>
       <c r="AF72" s="165" t="n">
-        <v>218.4052551918443</v>
+        <v>218.4052551918442</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>286.4361832395896</v>
+        <v>286.4361832395897</v>
       </c>
       <c r="AH72" s="166" t="n">
         <v>448.434226724071</v>
@@ -7807,49 +7807,49 @@
         </is>
       </c>
       <c r="C73" s="155" t="n">
-        <v>47.2804736992541</v>
+        <v>47.28047369925407</v>
       </c>
       <c r="D73" s="156" t="n">
-        <v>58.658378389092</v>
+        <v>58.65837838909199</v>
       </c>
       <c r="E73" s="156" t="n">
-        <v>69.86823003427473</v>
+        <v>69.86823003427469</v>
       </c>
       <c r="F73" s="156" t="n">
-        <v>81.15113088855017</v>
+        <v>81.15113088855016</v>
       </c>
       <c r="G73" s="157" t="n">
-        <v>93.4566075326219</v>
+        <v>93.45660753262186</v>
       </c>
       <c r="H73" s="155" t="n">
-        <v>47.2804736992541</v>
+        <v>47.28047369925407</v>
       </c>
       <c r="I73" s="156" t="n">
-        <v>58.658378389092</v>
+        <v>58.65837838909199</v>
       </c>
       <c r="J73" s="156" t="n">
-        <v>69.86823003427473</v>
+        <v>69.86823003427469</v>
       </c>
       <c r="K73" s="156" t="n">
-        <v>81.15113088855017</v>
+        <v>81.15113088855016</v>
       </c>
       <c r="L73" s="157" t="n">
-        <v>93.4566075326219</v>
+        <v>93.45660753262186</v>
       </c>
       <c r="M73" s="158" t="n">
-        <v>204.6782409735905</v>
+        <v>204.6782409735904</v>
       </c>
       <c r="N73" s="159" t="n">
-        <v>260.5306426687525</v>
+        <v>260.5306426687524</v>
       </c>
       <c r="O73" s="159" t="n">
-        <v>319.7497156239127</v>
+        <v>319.7497156239124</v>
       </c>
       <c r="P73" s="159" t="n">
         <v>378.9172421086479</v>
       </c>
       <c r="Q73" s="160" t="n">
-        <v>445.2245594222547</v>
+        <v>445.2245594222545</v>
       </c>
       <c r="S73" s="32" t="inlineStr">
         <is>
@@ -7857,49 +7857,49 @@
         </is>
       </c>
       <c r="T73" s="155" t="n">
-        <v>10.21491715724626</v>
+        <v>10.21491715724625</v>
       </c>
       <c r="U73" s="156" t="n">
         <v>12.67310644208778</v>
       </c>
       <c r="V73" s="156" t="n">
-        <v>15.094987970368</v>
+        <v>15.09498797036799</v>
       </c>
       <c r="W73" s="156" t="n">
         <v>17.53265173518059</v>
       </c>
       <c r="X73" s="157" t="n">
-        <v>20.19124236815906</v>
+        <v>20.19124236815905</v>
       </c>
       <c r="Y73" s="155" t="n">
-        <v>10.21491715724626</v>
+        <v>10.21491715724625</v>
       </c>
       <c r="Z73" s="156" t="n">
         <v>12.67310644208778</v>
       </c>
       <c r="AA73" s="156" t="n">
-        <v>15.094987970368</v>
+        <v>15.09498797036799</v>
       </c>
       <c r="AB73" s="156" t="n">
         <v>17.53265173518059</v>
       </c>
       <c r="AC73" s="157" t="n">
-        <v>20.19124236815906</v>
+        <v>20.19124236815905</v>
       </c>
       <c r="AD73" s="158" t="n">
-        <v>204.6782409735905</v>
+        <v>204.6782409735904</v>
       </c>
       <c r="AE73" s="159" t="n">
-        <v>260.5306426687525</v>
+        <v>260.5306426687524</v>
       </c>
       <c r="AF73" s="159" t="n">
-        <v>319.7497156239127</v>
+        <v>319.7497156239124</v>
       </c>
       <c r="AG73" s="159" t="n">
         <v>378.9172421086479</v>
       </c>
       <c r="AH73" s="160" t="n">
-        <v>445.2245594222547</v>
+        <v>445.2245594222545</v>
       </c>
     </row>
     <row r="74" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -7909,49 +7909,49 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>3.22255614955571</v>
+        <v>3.222556149555709</v>
       </c>
       <c r="D74" s="180" t="n">
         <v>3.178242892004288</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>3.583114384120007</v>
+        <v>3.583114384120005</v>
       </c>
       <c r="F74" s="180" t="n">
         <v>4.450508379994656</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>5.896886601481765</v>
+        <v>5.896886601481764</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>3.22255614955571</v>
+        <v>3.222556149555709</v>
       </c>
       <c r="I74" s="180" t="n">
         <v>3.178242892004288</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>3.583114384120007</v>
+        <v>3.583114384120005</v>
       </c>
       <c r="K74" s="180" t="n">
         <v>4.450508379994656</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>5.896886601481765</v>
+        <v>5.896886601481764</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>508.8382780749861</v>
+        <v>508.8382780749859</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>473.5212455639916</v>
+        <v>473.5212455639915</v>
       </c>
       <c r="O74" s="183" t="n">
-        <v>538.154970815757</v>
+        <v>538.1549708157565</v>
       </c>
       <c r="P74" s="183" t="n">
         <v>665.3534253482376</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>893.6587861463256</v>
+        <v>893.6587861463254</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,49 +7959,49 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>3.037699497594834</v>
+        <v>3.037699497594833</v>
       </c>
       <c r="U74" s="186" t="n">
         <v>2.985429693164918</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>3.367357705132321</v>
+        <v>3.367357705132318</v>
       </c>
       <c r="W74" s="186" t="n">
         <v>4.186778357137026</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>5.543765441097113</v>
+        <v>5.543765441097111</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>3.037699497594834</v>
+        <v>3.037699497594833</v>
       </c>
       <c r="Z74" s="186" t="n">
         <v>2.985429693164918</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>3.367357705132321</v>
+        <v>3.367357705132318</v>
       </c>
       <c r="AB74" s="186" t="n">
         <v>4.186778357137026</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>5.543765441097113</v>
+        <v>5.543765441097111</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>508.8382780749861</v>
+        <v>508.8382780749859</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>473.5212455639916</v>
+        <v>473.5212455639915</v>
       </c>
       <c r="AF74" s="189" t="n">
-        <v>538.154970815757</v>
+        <v>538.1549708157565</v>
       </c>
       <c r="AG74" s="189" t="n">
         <v>665.3534253482376</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>893.6587861463256</v>
+        <v>893.6587861463254</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,40 +8260,40 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>407.9991796458245</v>
+        <v>407.9991796458243</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>492.2486978246035</v>
+        <v>492.2486978246034</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>544.0612888046369</v>
+        <v>544.0612888046368</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>585.1531932803401</v>
+        <v>585.15319328034</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>579.3291513375884</v>
+        <v>579.3291513375882</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>407.9991796458245</v>
+        <v>407.9991796458243</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>492.2486978246035</v>
+        <v>492.2486978246034</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>544.0612888046369</v>
+        <v>544.0612888046368</v>
       </c>
       <c r="K79" s="149" t="n">
         <v>585.15319328034</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>579.3291513375883</v>
+        <v>579.3291513375882</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>28471.69447884347</v>
+        <v>28471.69447884346</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>28075.36223424783</v>
+        <v>28075.36223424782</v>
       </c>
       <c r="O79" s="152" t="n">
         <v>28127.48764370188</v>
@@ -8302,7 +8302,7 @@
         <v>26068.54881481979</v>
       </c>
       <c r="Q79" s="153" t="n">
-        <v>26060.96276865009</v>
+        <v>26060.96276865008</v>
       </c>
       <c r="S79" s="21" t="inlineStr">
         <is>
@@ -8310,40 +8310,40 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>412.8612179409373</v>
+        <v>412.8612179409371</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>498.1147194710693</v>
+        <v>498.1147194710692</v>
       </c>
       <c r="V79" s="149" t="n">
         <v>550.5447499315757</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>592.1263377771166</v>
+        <v>592.1263377771165</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>586.2328919816841</v>
+        <v>586.2328919816839</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>412.8612179409373</v>
+        <v>412.8612179409371</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>498.1147194710693</v>
+        <v>498.1147194710692</v>
       </c>
       <c r="AA79" s="149" t="n">
         <v>550.5447499315757</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>592.1263377771166</v>
+        <v>592.1263377771165</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>586.2328919816841</v>
+        <v>586.2328919816839</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>28471.69447884347</v>
+        <v>28471.69447884346</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>28075.36223424783</v>
+        <v>28075.36223424782</v>
       </c>
       <c r="AF79" s="152" t="n">
         <v>28127.48764370188</v>
@@ -8352,7 +8352,7 @@
         <v>26068.54881481979</v>
       </c>
       <c r="AH79" s="153" t="n">
-        <v>26060.96276865009</v>
+        <v>26060.96276865008</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" thickBot="1">
@@ -8368,7 +8368,7 @@
         <v>1293.592944167114</v>
       </c>
       <c r="E80" s="156" t="n">
-        <v>1392.462090817564</v>
+        <v>1392.462090817563</v>
       </c>
       <c r="F80" s="156" t="n">
         <v>1571.143934548078</v>
@@ -8383,13 +8383,13 @@
         <v>1293.592944167114</v>
       </c>
       <c r="J80" s="156" t="n">
-        <v>1392.462090817564</v>
+        <v>1392.462090817563</v>
       </c>
       <c r="K80" s="156" t="n">
         <v>1571.143934548078</v>
       </c>
       <c r="L80" s="157" t="n">
-        <v>1662.768847830453</v>
+        <v>1662.768847830454</v>
       </c>
       <c r="M80" s="158" t="n">
         <v>26612.99924137126</v>
@@ -8404,7 +8404,7 @@
         <v>32903.13302468607</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>35414.66909960086</v>
+        <v>35414.66909960087</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>32903.13302468607</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>35414.66909960086</v>
+        <v>35414.66909960087</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8464,46 +8464,46 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>586.1663633869907</v>
+        <v>586.1663633869905</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>712.6484327758648</v>
+        <v>712.6484327758646</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>795.2989800324136</v>
+        <v>795.2989800324134</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>900.4395358625893</v>
+        <v>900.4395358625892</v>
       </c>
       <c r="G81" s="163" t="n">
         <v>927.4673545100135</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>586.1663633869907</v>
+        <v>586.1663633869905</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>712.6484327758648</v>
+        <v>712.6484327758646</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>795.2989800324136</v>
+        <v>795.2989800324134</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>900.4395358625893</v>
+        <v>900.4395358625892</v>
       </c>
       <c r="L81" s="163" t="n">
         <v>927.4673545100135</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>55084.69372021473</v>
+        <v>55084.69372021472</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>56066.13221666663</v>
+        <v>56066.13221666662</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>58414.6314174279</v>
+        <v>58414.63141742788</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>58971.68183950586</v>
+        <v>58971.68183950585</v>
       </c>
       <c r="Q81" s="166" t="n">
         <v>61475.63186825095</v>
@@ -8514,46 +8514,46 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>591.6790432318553</v>
+        <v>591.6790432318551</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>719.2284211311348</v>
+        <v>719.2284211311347</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>802.4788756246135</v>
+        <v>802.4788756246132</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>908.361658158693</v>
+        <v>908.3616581586929</v>
       </c>
       <c r="X81" s="163" t="n">
         <v>935.6131946901389</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>591.6790432318553</v>
+        <v>591.6790432318551</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>719.2284211311348</v>
+        <v>719.2284211311347</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>802.4788756246135</v>
+        <v>802.4788756246132</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>908.361658158693</v>
+        <v>908.3616581586929</v>
       </c>
       <c r="AC81" s="163" t="n">
         <v>935.6131946901389</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>55084.69372021473</v>
+        <v>55084.69372021472</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>56066.13221666663</v>
+        <v>56066.13221666662</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>58414.6314174279</v>
+        <v>58414.63141742788</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>58971.68183950586</v>
+        <v>58971.68183950585</v>
       </c>
       <c r="AH81" s="166" t="n">
         <v>61475.63186825095</v>
@@ -8566,7 +8566,7 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>947.0605786236082</v>
+        <v>947.0605786236081</v>
       </c>
       <c r="D82" s="156" t="n">
         <v>1033.849289750276</v>
@@ -8578,10 +8578,10 @@
         <v>1208.316346220492</v>
       </c>
       <c r="G82" s="157" t="n">
-        <v>1274.779506932834</v>
+        <v>1274.779506932835</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>947.0605786236081</v>
+        <v>947.060578623608</v>
       </c>
       <c r="I82" s="156" t="n">
         <v>1033.849289750276</v>
@@ -8593,10 +8593,10 @@
         <v>1208.316346220492</v>
       </c>
       <c r="L82" s="157" t="n">
-        <v>1274.779506932834</v>
+        <v>1274.779506932835</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>56440.48883384247</v>
+        <v>56440.48883384246</v>
       </c>
       <c r="N82" s="159" t="n">
         <v>68103.75309619487</v>
@@ -8605,7 +8605,7 @@
         <v>80385.61208921993</v>
       </c>
       <c r="P82" s="159" t="n">
-        <v>95866.80313029894</v>
+        <v>95866.80313029897</v>
       </c>
       <c r="Q82" s="160" t="n">
         <v>102620.0729552573</v>
@@ -8625,10 +8625,10 @@
         <v>1220.924288618642</v>
       </c>
       <c r="W82" s="156" t="n">
-        <v>1324.406279348577</v>
+        <v>1324.406279348578</v>
       </c>
       <c r="X82" s="157" t="n">
-        <v>1397.254939939913</v>
+        <v>1397.254939939914</v>
       </c>
       <c r="Y82" s="155" t="n">
         <v>1038.050160602331</v>
@@ -8640,13 +8640,13 @@
         <v>1220.924288618642</v>
       </c>
       <c r="AB82" s="156" t="n">
-        <v>1324.406279348577</v>
+        <v>1324.406279348578</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>1397.254939939913</v>
+        <v>1397.254939939914</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>56440.48883384247</v>
+        <v>56440.48883384246</v>
       </c>
       <c r="AE82" s="159" t="n">
         <v>68103.75309619487</v>
@@ -8655,7 +8655,7 @@
         <v>80385.61208921993</v>
       </c>
       <c r="AG82" s="159" t="n">
-        <v>95866.80313029894</v>
+        <v>95866.80313029897</v>
       </c>
       <c r="AH82" s="160" t="n">
         <v>102620.0729552573</v>
@@ -8668,34 +8668,34 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>726.2175229297258</v>
+        <v>726.2175229297255</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>859.0284422615587</v>
+        <v>859.0284422615586</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>953.1969568453584</v>
+        <v>953.1969568453583</v>
       </c>
       <c r="F83" s="162" t="n">
         <v>1069.095711027092</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>1117.943115606288</v>
+        <v>1117.943115606289</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>726.2175229297258</v>
+        <v>726.2175229297255</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>859.0284422615587</v>
+        <v>859.0284422615586</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>953.1969568453584</v>
+        <v>953.1969568453583</v>
       </c>
       <c r="K83" s="162" t="n">
         <v>1069.095711027092</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>1117.943115606288</v>
+        <v>1117.943115606289</v>
       </c>
       <c r="M83" s="164" t="n">
         <v>111525.1825540572</v>
@@ -8718,10 +8718,10 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>756.2537599883486</v>
+        <v>756.2537599883484</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>899.4363812986289</v>
+        <v>899.4363812986288</v>
       </c>
       <c r="V83" s="162" t="n">
         <v>1001.208550965399</v>
@@ -8733,10 +8733,10 @@
         <v>1179.269456006546</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>756.2537599883486</v>
+        <v>756.2537599883484</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>899.4363812986289</v>
+        <v>899.4363812986288</v>
       </c>
       <c r="AA83" s="162" t="n">
         <v>1001.208550965399</v>
@@ -8770,49 +8770,49 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>367.9492727259787</v>
+        <v>367.9492727259786</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>410.9473790975439</v>
+        <v>410.9473790975438</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>457.0923312475085</v>
+        <v>457.0923312475084</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>500.9150699099199</v>
+        <v>500.9150699099197</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>547.4100692171795</v>
+        <v>547.4100692171792</v>
       </c>
       <c r="H84" s="155" t="n">
         <v>367.9492727259787</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>410.9473790975439</v>
+        <v>410.9473790975437</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>457.0923312475085</v>
+        <v>457.0923312475084</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>500.9150699099199</v>
+        <v>500.9150699099197</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>547.4100692171794</v>
+        <v>547.4100692171793</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>1592.860731220918</v>
+        <v>1592.860731220917</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>1825.218966490081</v>
+        <v>1825.21896649008</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>2091.868405118663</v>
+        <v>2091.868405118662</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>2338.912036624588</v>
+        <v>2338.912036624587</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>2607.845644359087</v>
+        <v>2607.845644359086</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,13 +8820,13 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>79.49521324326703</v>
+        <v>79.495213243267</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>88.78492758280271</v>
+        <v>88.78492758280267</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>98.7545160102642</v>
+        <v>98.75451601026415</v>
       </c>
       <c r="W84" s="156" t="n">
         <v>108.2223916472049</v>
@@ -8835,13 +8835,13 @@
         <v>118.2676075469215</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>79.49521324326703</v>
+        <v>79.495213243267</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>88.78492758280271</v>
+        <v>88.78492758280267</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>98.7545160102642</v>
+        <v>98.75451601026415</v>
       </c>
       <c r="AB84" s="156" t="n">
         <v>108.2223916472049</v>
@@ -8850,19 +8850,19 @@
         <v>118.2676075469215</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>1592.860731220918</v>
+        <v>1592.860731220917</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>1825.218966490081</v>
+        <v>1825.21896649008</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>2091.868405118663</v>
+        <v>2091.868405118662</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>2338.912036624588</v>
+        <v>2338.912036624587</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>2607.845644359087</v>
+        <v>2607.845644359086</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,34 +8872,34 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>716.3950939260163</v>
+        <v>716.3950939260161</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>845.6707029612517</v>
+        <v>845.6707029612515</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>938.0802560177989</v>
+        <v>938.0802560177987</v>
       </c>
       <c r="F85" s="180" t="n">
         <v>1051.349998170884</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>1100.008133319518</v>
+        <v>1100.008133319519</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>716.3950939260163</v>
+        <v>716.3950939260161</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>845.6707029612517</v>
+        <v>845.6707029612515</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>938.0802560177989</v>
+        <v>938.0802560177987</v>
       </c>
       <c r="K85" s="180" t="n">
         <v>1051.349998170884</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>1100.008133319518</v>
+        <v>1100.008133319519</v>
       </c>
       <c r="M85" s="182" t="n">
         <v>113118.0432852781</v>
@@ -8922,13 +8922,13 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>675.3002634875712</v>
+        <v>675.300263487571</v>
       </c>
       <c r="U85" s="186" t="n">
         <v>794.3667344027411</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>881.5938983510378</v>
+        <v>881.5938983510376</v>
       </c>
       <c r="W85" s="186" t="n">
         <v>989.0486754062005</v>
@@ -8937,13 +8937,13 @@
         <v>1034.136738001735</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>675.3002634875712</v>
+        <v>675.300263487571</v>
       </c>
       <c r="Z85" s="186" t="n">
         <v>794.3667344027411</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>881.5938983510378</v>
+        <v>881.5938983510376</v>
       </c>
       <c r="AB85" s="186" t="n">
         <v>989.0486754062005</v>
